--- a/data/trans_dic/P16A15-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P16A15-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para bajar el colesterol en las dos últimas semanas</t>
+          <t>Población que ha consumido medicinas para bajar el colesterol en las dos últimas semanas (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,82; 8,18</t>
+          <t>3,93; 8,39</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,35; 12,44</t>
+          <t>6,39; 12,59</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,1; 11,71</t>
+          <t>5,99; 11,56</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9,37; 14,69</t>
+          <t>9,53; 14,76</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,33; 7,66</t>
+          <t>2,66; 7,52</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,29; 8,92</t>
+          <t>3,32; 9,04</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,36; 7,44</t>
+          <t>2,16; 7,32</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,55; 13,18</t>
+          <t>8,36; 13,15</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,7; 7,24</t>
+          <t>3,78; 7,05</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,66; 9,87</t>
+          <t>5,65; 9,88</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,7; 8,68</t>
+          <t>4,94; 8,6</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9,67; 13,02</t>
+          <t>9,62; 13,05</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,49; 8,26</t>
+          <t>3,23; 7,8</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,64; 12,59</t>
+          <t>6,61; 12,39</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,63; 11,49</t>
+          <t>5,87; 11,31</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11,07; 17,11</t>
+          <t>11,19; 17,27</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,56; 5,26</t>
+          <t>1,51; 5,36</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,2; 10,19</t>
+          <t>3,91; 9,95</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,87; 9,54</t>
+          <t>4,17; 9,53</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,2; 11,69</t>
+          <t>7,16; 11,9</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,81; 5,88</t>
+          <t>2,94; 5,9</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,06; 10,24</t>
+          <t>6,04; 10,37</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,44; 9,44</t>
+          <t>5,51; 9,54</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,86; 13,73</t>
+          <t>10,12; 13,9</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,9; 7,75</t>
+          <t>3,9; 7,96</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,41; 14,78</t>
+          <t>9,42; 14,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,83; 14,34</t>
+          <t>8,92; 14,6</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,27; 15,87</t>
+          <t>3,63; 16,46</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,52; 11,29</t>
+          <t>3,38; 10,94</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,33; 12,86</t>
+          <t>4,96; 11,96</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,64; 19,43</t>
+          <t>7,49; 18,69</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12,76; 20,65</t>
+          <t>12,65; 21,27</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,34; 7,77</t>
+          <t>4,24; 7,77</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8,81; 13,26</t>
+          <t>8,59; 13,01</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9,37; 14,49</t>
+          <t>9,33; 14,48</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,45; 16,21</t>
+          <t>4,39; 16,03</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,12; 9,01</t>
+          <t>6,12; 9,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,17; 14,09</t>
+          <t>10,21; 14,2</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,58; 12,31</t>
+          <t>8,6; 12,18</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12,1; 16,06</t>
+          <t>12,15; 16,08</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,31; 7,53</t>
+          <t>4,36; 7,68</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,11; 10,36</t>
+          <t>6,28; 10,52</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,07; 8,53</t>
+          <t>5,04; 8,47</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,24; 62,52</t>
+          <t>10,36; 63,35</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,84; 7,94</t>
+          <t>5,87; 8,1</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9,11; 12,03</t>
+          <t>9,08; 12,08</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,66; 10,09</t>
+          <t>7,55; 10,25</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12,2; 46,72</t>
+          <t>12,21; 48,38</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,89; 7,04</t>
+          <t>3,04; 7,18</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,92; 14,56</t>
+          <t>9,01; 14,65</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,89; 13,79</t>
+          <t>9,21; 13,96</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9,53; 15,14</t>
+          <t>9,6; 15,16</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,91; 10,5</t>
+          <t>5,69; 10,25</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,43; 18,09</t>
+          <t>12,77; 18,1</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,82; 16,27</t>
+          <t>11,27; 16,19</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>12,86; 20,21</t>
+          <t>12,9; 20,11</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,05; 8,32</t>
+          <t>5,2; 8,43</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11,9; 16,03</t>
+          <t>11,91; 15,82</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10,84; 14,47</t>
+          <t>10,81; 14,48</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>12,77; 17,21</t>
+          <t>12,54; 17,3</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,85</t>
+          <t>0,29; 2,68</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,04</t>
+          <t>0,0; 4,36</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,88</t>
+          <t>0,0; 2,64</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,61; 3,41</t>
+          <t>0,6; 3,45</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9,82; 13,33</t>
+          <t>9,74; 13,6</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>15,46; 20,23</t>
+          <t>15,64; 20,54</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>13,66; 18,5</t>
+          <t>13,69; 18,58</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>14,96; 19,41</t>
+          <t>15,18; 19,16</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8,04; 11,1</t>
+          <t>8,05; 11,03</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>12,81; 16,76</t>
+          <t>12,87; 16,8</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>11,11; 14,99</t>
+          <t>10,99; 14,9</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>11,67; 14,97</t>
+          <t>11,68; 15,03</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,97; 6,66</t>
+          <t>5,04; 6,67</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9,16; 11,45</t>
+          <t>9,26; 11,42</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8,51; 10,46</t>
+          <t>8,37; 10,37</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9,07; 13,03</t>
+          <t>8,85; 12,98</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,92; 8,89</t>
+          <t>7,04; 8,87</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,18; 13,45</t>
+          <t>11,2; 13,61</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,95; 12,08</t>
+          <t>9,87; 12,12</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>13,55; 33,88</t>
+          <t>13,57; 34,32</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6,29; 7,5</t>
+          <t>6,25; 7,47</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10,5; 12,08</t>
+          <t>10,55; 12,09</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9,5; 11,02</t>
+          <t>9,4; 10,98</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>12,39; 22,88</t>
+          <t>12,27; 24,53</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para bajar el colesterol en las dos últimas semanas</t>
+          <t>Población que ha consumido medicinas para bajar el colesterol en las dos últimas semanas (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>18104; 38742</t>
+          <t>18630; 39761</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>27723; 54291</t>
+          <t>27886; 54942</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>26194; 50247</t>
+          <t>25685; 49619</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>47314; 74228</t>
+          <t>48129; 74592</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>7135; 23484</t>
+          <t>8145; 23058</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10339; 28060</t>
+          <t>10455; 28418</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8187; 25816</t>
+          <t>7490; 25419</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>38277; 58992</t>
+          <t>37391; 58846</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>28913; 56491</t>
+          <t>29474; 55002</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>42528; 74077</t>
+          <t>42435; 74162</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>36465; 67392</t>
+          <t>38350; 66711</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>92102; 124057</t>
+          <t>91672; 124357</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12807; 30323</t>
+          <t>11838; 28604</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>27683; 52512</t>
+          <t>27565; 51649</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>21250; 43344</t>
+          <t>22147; 42664</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>50063; 77367</t>
+          <t>50620; 78100</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5802; 19559</t>
+          <t>5611; 19917</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14083; 34170</t>
+          <t>13103; 33368</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14400; 35511</t>
+          <t>15515; 35488</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>27530; 44710</t>
+          <t>27379; 45520</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>20771; 43413</t>
+          <t>21700; 43574</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>45580; 77053</t>
+          <t>45471; 77984</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>40742; 70787</t>
+          <t>41323; 71477</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>82335; 114578</t>
+          <t>84510; 115999</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>21127; 42055</t>
+          <t>21141; 43149</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>59146; 92842</t>
+          <t>59163; 93629</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>46064; 74847</t>
+          <t>46567; 76195</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>21877; 106085</t>
+          <t>24287; 109976</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5910; 18950</t>
+          <t>5666; 18362</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13746; 33174</t>
+          <t>12794; 30862</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12695; 32284</t>
+          <t>12437; 31048</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>21304; 34462</t>
+          <t>21110; 35510</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>30856; 55148</t>
+          <t>30125; 55199</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>78059; 117533</t>
+          <t>76118; 115333</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>64462; 99692</t>
+          <t>64211; 99658</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>37136; 135419</t>
+          <t>36646; 133905</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>75768; 111518</t>
+          <t>75736; 111400</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>117754; 163218</t>
+          <t>118280; 164438</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>98605; 141574</t>
+          <t>98898; 140040</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>125198; 166189</t>
+          <t>125731; 166392</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>30750; 53760</t>
+          <t>31108; 54867</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>46830; 79429</t>
+          <t>48172; 80617</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>41847; 70451</t>
+          <t>41639; 69973</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>100128; 611136</t>
+          <t>101283; 619281</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>114069; 155101</t>
+          <t>114694; 158105</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>175288; 231508</t>
+          <t>174843; 232605</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>151235; 199342</t>
+          <t>149219; 202479</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>245574; 940145</t>
+          <t>245688; 973535</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>10107; 24615</t>
+          <t>10641; 25097</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>45524; 74352</t>
+          <t>46022; 74801</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>55157; 85581</t>
+          <t>57150; 86640</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>45154; 71777</t>
+          <t>45524; 71851</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>33640; 59730</t>
+          <t>32334; 58308</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>94273; 137192</t>
+          <t>96802; 137230</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>79865; 120127</t>
+          <t>83196; 119557</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>107905; 169537</t>
+          <t>108222; 168734</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>46386; 76424</t>
+          <t>47740; 77453</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>150991; 203422</t>
+          <t>151084; 200676</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>147309; 196614</t>
+          <t>146861; 196730</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>167660; 225949</t>
+          <t>164598; 227118</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>878; 8496</t>
+          <t>877; 7978</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 10742</t>
+          <t>0; 11585</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 8279</t>
+          <t>0; 7590</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1469; 8199</t>
+          <t>1446; 8301</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>122614; 166422</t>
+          <t>121621; 169799</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>171044; 223794</t>
+          <t>173070; 227257</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>147783; 200224</t>
+          <t>148118; 201074</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>113732; 147533</t>
+          <t>115386; 145659</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>124318; 171656</t>
+          <t>124457; 170631</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>175808; 229953</t>
+          <t>176530; 230550</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>152164; 205183</t>
+          <t>150502; 204067</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>116793; 149773</t>
+          <t>116868; 150388</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>162631; 217863</t>
+          <t>164647; 218093</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>313100; 391299</t>
+          <t>316306; 389987</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>288285; 354139</t>
+          <t>283223; 351079</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>306014; 439828</t>
+          <t>298733; 437922</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>233841; 300449</t>
+          <t>237666; 299767</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>395630; 475938</t>
+          <t>396206; 481647</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>351381; 426558</t>
+          <t>348619; 428172</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>484184; 1210637</t>
+          <t>484840; 1226402</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>417975; 498433</t>
+          <t>415522; 496595</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>730485; 839948</t>
+          <t>733799; 840851</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>656883; 762422</t>
+          <t>650291; 759840</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>860897; 1590199</t>
+          <t>852789; 1704581</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16A15-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P16A15-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,18%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,93; 8,39</t>
+          <t>3,98; 8,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,39; 12,59</t>
+          <t>6,42; 12,58</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,99; 11,56</t>
+          <t>6,05; 11,9</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9,53; 14,76</t>
+          <t>9,68; 14,44</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,66; 7,52</t>
+          <t>2,36; 7,38</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,32; 9,04</t>
+          <t>3,3; 8,84</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,16; 7,32</t>
+          <t>2,24; 7,2</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,36; 13,15</t>
+          <t>8,3; 13,19</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,78; 7,05</t>
+          <t>3,74; 7,14</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,65; 9,88</t>
+          <t>5,72; 10,05</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,94; 8,6</t>
+          <t>4,8; 8,59</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9,62; 13,05</t>
+          <t>9,61; 12,95</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,67%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,23; 7,8</t>
+          <t>3,49; 8,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,61; 12,39</t>
+          <t>6,32; 12,25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,87; 11,31</t>
+          <t>5,63; 11,51</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11,19; 17,27</t>
+          <t>11,14; 17,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,51; 5,36</t>
+          <t>1,42; 5,38</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,91; 9,95</t>
+          <t>4,03; 9,99</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,17; 9,53</t>
+          <t>4,06; 9,73</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,16; 11,9</t>
+          <t>7,04; 11,53</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,94; 5,9</t>
+          <t>2,87; 5,81</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,04; 10,37</t>
+          <t>6,09; 10,27</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,51; 9,54</t>
+          <t>5,4; 9,29</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10,12; 13,9</t>
+          <t>9,82; 13,68</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>14,91%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,9; 7,96</t>
+          <t>3,88; 8,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,42; 14,9</t>
+          <t>9,19; 14,73</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,92; 14,6</t>
+          <t>9,02; 14,44</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,63; 16,46</t>
+          <t>11,77; 17,79</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,38; 10,94</t>
+          <t>3,54; 11,53</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,96; 11,96</t>
+          <t>4,98; 12,05</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,49; 18,69</t>
+          <t>7,81; 19,48</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12,65; 21,27</t>
+          <t>12,5; 20,99</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,24; 7,77</t>
+          <t>4,26; 7,84</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8,59; 13,01</t>
+          <t>8,56; 13,2</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9,33; 14,48</t>
+          <t>9,37; 14,35</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,39; 16,03</t>
+          <t>12,63; 17,4</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>12,34%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,12; 9,0</t>
+          <t>6,05; 8,95</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,21; 14,2</t>
+          <t>10,1; 14,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,6; 12,18</t>
+          <t>8,74; 12,08</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12,15; 16,08</t>
+          <t>11,84; 15,47</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,36; 7,68</t>
+          <t>4,2; 7,52</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,28; 10,52</t>
+          <t>6,0; 10,46</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,04; 8,47</t>
+          <t>5,13; 8,81</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,36; 63,35</t>
+          <t>9,25; 12,62</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,87; 8,1</t>
+          <t>5,83; 8,15</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9,08; 12,08</t>
+          <t>8,92; 11,91</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,55; 10,25</t>
+          <t>7,5; 10,06</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12,21; 48,38</t>
+          <t>11,04; 13,64</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,74%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,04; 7,18</t>
+          <t>2,84; 7,28</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,01; 14,65</t>
+          <t>8,82; 14,53</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9,21; 13,96</t>
+          <t>9,03; 14,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9,6; 15,16</t>
+          <t>8,94; 13,44</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,69; 10,25</t>
+          <t>5,89; 10,31</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,77; 18,1</t>
+          <t>12,84; 18,24</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,27; 16,19</t>
+          <t>11,22; 16,6</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>12,9; 20,11</t>
+          <t>17,21; 21,44</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,2; 8,43</t>
+          <t>5,17; 8,55</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11,91; 15,82</t>
+          <t>11,85; 15,87</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10,81; 14,48</t>
+          <t>10,67; 14,43</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>12,54; 17,3</t>
+          <t>14,31; 17,35</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,42%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,68</t>
+          <t>0,29; 2,65</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,36</t>
+          <t>0,0; 4,04</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,64</t>
+          <t>0,0; 2,97</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,6; 3,45</t>
+          <t>0,56; 3,5</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9,74; 13,6</t>
+          <t>9,95; 13,37</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>15,64; 20,54</t>
+          <t>15,53; 20,36</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>13,69; 18,58</t>
+          <t>13,95; 18,56</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>15,18; 19,16</t>
+          <t>14,87; 18,74</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8,05; 11,03</t>
+          <t>7,99; 11,04</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>12,87; 16,8</t>
+          <t>12,7; 16,45</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>10,99; 14,9</t>
+          <t>10,99; 14,97</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>11,68; 15,03</t>
+          <t>11,82; 15,19</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>13,16%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,04; 6,67</t>
+          <t>5,03; 6,57</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9,26; 11,42</t>
+          <t>9,18; 11,33</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8,37; 10,37</t>
+          <t>8,5; 10,41</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8,85; 12,98</t>
+          <t>11,15; 13,18</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,04; 8,87</t>
+          <t>7,07; 8,92</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,2; 13,61</t>
+          <t>11,16; 13,54</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,87; 12,12</t>
+          <t>9,92; 12,12</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>13,57; 34,32</t>
+          <t>13,29; 15,05</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6,25; 7,47</t>
+          <t>6,22; 7,46</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10,55; 12,09</t>
+          <t>10,57; 12,09</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9,4; 10,98</t>
+          <t>9,5; 11,01</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>12,27; 24,53</t>
+          <t>12,48; 13,86</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>59764</t>
+          <t>65036</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>46976</t>
+          <t>51134</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>106739</t>
+          <t>116170</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>18630; 39761</t>
+          <t>18853; 41187</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>27886; 54942</t>
+          <t>28030; 54888</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>25685; 49619</t>
+          <t>25949; 51067</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>48129; 74592</t>
+          <t>53311; 79525</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>8145; 23058</t>
+          <t>7233; 22644</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10455; 28418</t>
+          <t>10364; 27809</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7490; 25419</t>
+          <t>7776; 24977</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>37391; 58846</t>
+          <t>40537; 64417</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>29474; 55002</t>
+          <t>29185; 55757</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>42435; 74162</t>
+          <t>42941; 75424</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>38350; 66711</t>
+          <t>37260; 66644</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>91672; 124357</t>
+          <t>99833; 134598</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>62667</t>
+          <t>67018</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>35541</t>
+          <t>38709</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>98208</t>
+          <t>105727</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11838; 28604</t>
+          <t>12799; 29744</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>27565; 51649</t>
+          <t>26349; 51105</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>22147; 42664</t>
+          <t>21228; 43422</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>50620; 78100</t>
+          <t>53809; 82162</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5611; 19917</t>
+          <t>5294; 20012</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13103; 33368</t>
+          <t>13497; 33511</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15515; 35488</t>
+          <t>15101; 36210</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>27379; 45520</t>
+          <t>29796; 48791</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>21700; 43574</t>
+          <t>21226; 42898</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>45471; 77984</t>
+          <t>45815; 77239</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>41323; 71477</t>
+          <t>40471; 69594</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>84510; 115999</t>
+          <t>88994; 124035</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>63795</t>
+          <t>68113</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>27620</t>
+          <t>30182</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>91415</t>
+          <t>98295</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>21141; 43149</t>
+          <t>21041; 44199</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>59163; 93629</t>
+          <t>57760; 92547</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>46567; 76195</t>
+          <t>47057; 75371</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>24287; 109976</t>
+          <t>55490; 83923</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5666; 18362</t>
+          <t>5943; 19350</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12794; 30862</t>
+          <t>12841; 31088</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12437; 31048</t>
+          <t>12976; 32369</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>21110; 35510</t>
+          <t>23443; 39351</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>30125; 55199</t>
+          <t>30229; 55676</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>76118; 115333</t>
+          <t>75854; 116990</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>64211; 99658</t>
+          <t>64435; 98713</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>36646; 133905</t>
+          <t>83226; 114704</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>144714</t>
+          <t>153998</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>287807</t>
+          <t>91792</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>432521</t>
+          <t>245791</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>75736; 111400</t>
+          <t>74902; 110846</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>118280; 164438</t>
+          <t>116968; 164682</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>98898; 140040</t>
+          <t>100488; 138890</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>125731; 166392</t>
+          <t>133959; 175106</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>31108; 54867</t>
+          <t>30009; 53690</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>48172; 80617</t>
+          <t>46036; 80227</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>41639; 69973</t>
+          <t>42402; 72780</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>101283; 619281</t>
+          <t>79602; 108643</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>114694; 158105</t>
+          <t>113833; 159068</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>174843; 232605</t>
+          <t>171672; 229246</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>149219; 202479</t>
+          <t>148179; 198813</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>245688; 973535</t>
+          <t>220048; 271844</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>57448</t>
+          <t>60926</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>145586</t>
+          <t>159047</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>203034</t>
+          <t>219973</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>10641; 25097</t>
+          <t>9926; 25433</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>46022; 74801</t>
+          <t>45042; 74174</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>57150; 86640</t>
+          <t>56070; 86888</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>45524; 71851</t>
+          <t>50665; 76190</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>32334; 58308</t>
+          <t>33522; 58622</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>96802; 137230</t>
+          <t>97351; 138295</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>83196; 119557</t>
+          <t>82832; 122530</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>108222; 168734</t>
+          <t>142865; 177978</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>47740; 77453</t>
+          <t>47443; 78469</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>151084; 200676</t>
+          <t>150410; 201421</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>146861; 196730</t>
+          <t>144970; 196083</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>164598; 227118</t>
+          <t>199988; 242342</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3654</t>
+          <t>3643</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>129274</t>
+          <t>141332</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>132928</t>
+          <t>144975</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>877; 7978</t>
+          <t>873; 7904</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 11585</t>
+          <t>0; 10743</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 7590</t>
+          <t>0; 8515</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1446; 8301</t>
+          <t>1330; 8312</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>121621; 169799</t>
+          <t>124284; 166908</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>173070; 227257</t>
+          <t>171788; 225266</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>148118; 201074</t>
+          <t>150894; 200776</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>115386; 145659</t>
+          <t>125376; 158000</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>124457; 170631</t>
+          <t>123529; 170745</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>176530; 230550</t>
+          <t>174292; 225719</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>150502; 204067</t>
+          <t>150476; 204969</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>116868; 150388</t>
+          <t>127717; 164093</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>392041</t>
+          <t>418734</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>672804</t>
+          <t>512196</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>1064845</t>
+          <t>930931</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>164647; 218093</t>
+          <t>164427; 214944</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>316306; 389987</t>
+          <t>313448; 387081</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>283223; 351079</t>
+          <t>287889; 352557</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>298733; 437922</t>
+          <t>383820; 453558</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>237666; 299767</t>
+          <t>238703; 301162</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>396206; 481647</t>
+          <t>394921; 479310</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>348619; 428172</t>
+          <t>350503; 428172</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>484840; 1226402</t>
+          <t>482665; 546884</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>415522; 496595</t>
+          <t>413384; 496162</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>733799; 840851</t>
+          <t>735100; 840748</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>650291; 759840</t>
+          <t>657489; 761846</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>852789; 1704581</t>
+          <t>883201; 980171</t>
         </is>
       </c>
     </row>
